--- a/reports/excel/selenium-report.xlsx
+++ b/reports/excel/selenium-report.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="371">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -52,7 +52,7 @@
     <t>Additional Remarks</t>
   </si>
   <si>
-    <t>TC_9047</t>
+    <t>TC_1028</t>
   </si>
   <si>
     <t>Functional Testing</t>
@@ -73,7 +73,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.047Z</t>
+    <t>2026-06-23T04:30:11.028Z</t>
   </si>
   <si>
     <t>N/A</t>
@@ -82,445 +82,490 @@
     <t/>
   </si>
   <si>
-    <t>TC_9048</t>
+    <t>TC_1030</t>
   </si>
   <si>
     <t>TC_AUTH_002: should validate invalid login</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.048Z</t>
-  </si>
-  <si>
-    <t>TC_9049</t>
+    <t>2026-06-23T04:30:11.030Z</t>
   </si>
   <si>
     <t>TC_AUTH_003: should validate empty credentials</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.049Z</t>
-  </si>
-  <si>
-    <t>TC_9050</t>
+    <t>TC_1031</t>
   </si>
   <si>
     <t>TC_AUTH_004: should validate forgot password flow</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.050Z</t>
-  </si>
-  <si>
-    <t>TC_9052</t>
+    <t>2026-06-23T04:30:11.031Z</t>
+  </si>
+  <si>
+    <t>TC_1032</t>
   </si>
   <si>
     <t>TC_AUTH_005: should validate user registration</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.052Z</t>
-  </si>
-  <si>
-    <t>TC_9053</t>
+    <t>2026-06-23T04:30:11.032Z</t>
+  </si>
+  <si>
+    <t>TC_1034</t>
   </si>
   <si>
     <t>TC_AUTH_006: should handle duplicate account registration</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.053Z</t>
-  </si>
-  <si>
-    <t>TC_9054</t>
+    <t>2026-06-23T04:30:11.034Z</t>
+  </si>
+  <si>
+    <t>TC_1035</t>
   </si>
   <si>
     <t>TC_AUTH_007: should validate logout functionality</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.054Z</t>
+    <t>2026-06-23T04:30:11.035Z</t>
+  </si>
+  <si>
+    <t>TC_1036</t>
   </si>
   <si>
     <t>TC_AUTH_008: should handle session timeout</t>
   </si>
   <si>
-    <t>TC_9055</t>
+    <t>2026-06-23T04:30:11.036Z</t>
+  </si>
+  <si>
+    <t>TC_1037</t>
   </si>
   <si>
     <t>TC_AUTH_009: should validate login with unverified email</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.055Z</t>
-  </si>
-  <si>
-    <t>TC_9056</t>
+    <t>2026-06-23T04:30:11.037Z</t>
+  </si>
+  <si>
+    <t>TC_1038</t>
   </si>
   <si>
     <t>TC_AUTH_010: should validate login with suspended account</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.056Z</t>
-  </si>
-  <si>
-    <t>TC_9057</t>
+    <t>2026-06-23T04:30:11.038Z</t>
+  </si>
+  <si>
+    <t>TC_1039</t>
   </si>
   <si>
     <t>TC_AUTH_011: should validate password reset token expiration</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.057Z</t>
+    <t>2026-06-23T04:30:11.039Z</t>
   </si>
   <si>
     <t>TC_AUTH_012: should validate remember me functionality</t>
   </si>
   <si>
-    <t>TC_9059</t>
+    <t>TC_1041</t>
   </si>
   <si>
     <t>TC_CRUD_001: Create new record with valid data</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.059Z</t>
+    <t>2026-06-23T04:30:11.041Z</t>
+  </si>
+  <si>
+    <t>TC_1042</t>
   </si>
   <si>
     <t>TC_CRUD_002: Create new record with missing required fields</t>
   </si>
   <si>
-    <t>TC_9060</t>
+    <t>2026-06-23T04:30:11.042Z</t>
   </si>
   <si>
     <t>TC_CRUD_003: Read existing record details</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.060Z</t>
+    <t>TC_1043</t>
   </si>
   <si>
     <t>TC_CRUD_004: Read record list pagination</t>
   </si>
   <si>
-    <t>TC_9061</t>
+    <t>2026-06-23T04:30:11.043Z</t>
   </si>
   <si>
     <t>TC_CRUD_005: Update record with valid data</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.061Z</t>
+    <t>TC_1044</t>
   </si>
   <si>
     <t>TC_CRUD_006: Update record with invalid data</t>
   </si>
   <si>
-    <t>TC_9062</t>
+    <t>2026-06-23T04:30:11.044Z</t>
   </si>
   <si>
     <t>TC_CRUD_007: Delete existing record</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.062Z</t>
+    <t>TC_1045</t>
   </si>
   <si>
     <t>TC_CRUD_008: Cancel delete operation</t>
   </si>
   <si>
-    <t>TC_9063</t>
+    <t>2026-06-23T04:30:11.045Z</t>
   </si>
   <si>
     <t>TC_CRUD_009: Confirmation dialogs on delete</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.063Z</t>
+    <t>TC_1046</t>
   </si>
   <si>
     <t>TC_CRUD_010: Data persistence validation after refresh</t>
   </si>
   <si>
-    <t>TC_9064</t>
+    <t>2026-06-23T04:30:11.046Z</t>
   </si>
   <si>
     <t>TC_CRUD_011: Create record with duplicate unique key</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.064Z</t>
+    <t>TC_1047</t>
   </si>
   <si>
     <t>TC_CRUD_012: Read operation on non-existent record</t>
   </si>
   <si>
-    <t>TC_9065</t>
+    <t>2026-06-23T04:30:11.047Z</t>
   </si>
   <si>
     <t>TC_CRUD_013: Bulk delete records</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.065Z</t>
+    <t>TC_1048</t>
   </si>
   <si>
     <t>TC_CRUD_014: Bulk update records</t>
   </si>
   <si>
-    <t>TC_9066</t>
+    <t>2026-06-23T04:30:11.048Z</t>
   </si>
   <si>
     <t>TC_CRUD_015: File upload during create</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.066Z</t>
+    <t>TC_1049</t>
   </si>
   <si>
     <t>TC_CRUD_016: File download from read view</t>
   </si>
   <si>
-    <t>TC_9067</t>
+    <t>2026-06-23T04:30:11.049Z</t>
+  </si>
+  <si>
+    <t>TC_1050</t>
   </si>
   <si>
     <t>TC_CRUD_017: Record state transition</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.067Z</t>
+    <t>2026-06-23T04:30:11.050Z</t>
+  </si>
+  <si>
+    <t>TC_1051</t>
   </si>
   <si>
     <t>TC_CRUD_018: Inline editing in list view</t>
   </si>
   <si>
-    <t>TC_9068</t>
+    <t>2026-06-23T04:30:11.051Z</t>
+  </si>
+  <si>
+    <t>TC_1052</t>
   </si>
   <si>
     <t>TC_CRUD_019: Sort records by column</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.068Z</t>
-  </si>
-  <si>
-    <t>TC_9069</t>
+    <t>2026-06-23T04:30:11.052Z</t>
+  </si>
+  <si>
+    <t>TC_1053</t>
   </si>
   <si>
     <t>TC_CRUD_020: Filter records by criteria</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.069Z</t>
-  </si>
-  <si>
-    <t>TC_9070</t>
+    <t>2026-06-23T04:30:11.053Z</t>
+  </si>
+  <si>
+    <t>TC_1055</t>
   </si>
   <si>
     <t>TC_DASH_001: Dashboard loading</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.070Z</t>
+    <t>2026-06-23T04:30:11.055Z</t>
   </si>
   <si>
     <t>TC_DASH_002: Data rendering on widgets</t>
   </si>
   <si>
-    <t>TC_9071</t>
+    <t>TC_1056</t>
   </si>
   <si>
     <t>TC_DASH_003: Navigation cards clickability</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.071Z</t>
-  </si>
-  <si>
-    <t>TC_9072</t>
+    <t>2026-06-23T04:30:11.056Z</t>
+  </si>
+  <si>
+    <t>TC_1057</t>
   </si>
   <si>
     <t>TC_DASH_004: Widgets and metrics accuracy</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.072Z</t>
+    <t>2026-06-23T04:30:11.057Z</t>
+  </si>
+  <si>
+    <t>TC_1058</t>
   </si>
   <si>
     <t>TC_DASH_005: User profile access from dashboard</t>
   </si>
   <si>
+    <t>2026-06-23T04:30:11.058Z</t>
+  </si>
+  <si>
+    <t>TC_1059</t>
+  </si>
+  <si>
     <t>TC_DASH_006: Dashboard refresh behavior</t>
   </si>
   <si>
-    <t>TC_9073</t>
+    <t>2026-06-23T04:30:11.059Z</t>
   </si>
   <si>
     <t>TC_DASH_007: Sidebar toggle state persistence</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.073Z</t>
+    <t>TC_1060</t>
   </si>
   <si>
     <t>TC_DASH_008: Notifications panel open/close</t>
   </si>
   <si>
-    <t>TC_9074</t>
+    <t>2026-06-23T04:30:11.060Z</t>
   </si>
   <si>
     <t>TC_DASH_009: Recent activity feed updates</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.074Z</t>
+    <t>TC_1061</t>
   </si>
   <si>
     <t>TC_DASH_010: Quick action buttons functionality</t>
   </si>
   <si>
+    <t>2026-06-23T04:30:11.061Z</t>
+  </si>
+  <si>
+    <t>TC_1062</t>
+  </si>
+  <si>
     <t>TC_DASH_011: Data charts rendering</t>
   </si>
   <si>
-    <t>TC_9075</t>
+    <t>2026-06-23T04:30:11.062Z</t>
   </si>
   <si>
     <t>TC_DASH_012: Data charts tooltips</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.075Z</t>
-  </si>
-  <si>
     <t>TC_DASH_013: Dashboard layout responsiveness</t>
   </si>
   <si>
-    <t>TC_9076</t>
+    <t>TC_1063</t>
   </si>
   <si>
     <t>TC_DASH_014: Theme toggle effect on dashboard</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:09.076Z</t>
+    <t>2026-06-23T04:30:11.063Z</t>
   </si>
   <si>
     <t>TC_DASH_015: Loading spinners presence during data fetch</t>
   </si>
   <si>
-    <t>TC_2041</t>
+    <t>TC_0901</t>
   </si>
   <si>
     <t>should load the homepage</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:52.041Z</t>
-  </si>
-  <si>
-    <t>TC_2320</t>
+    <t>2026-06-23T04:31:00.901Z</t>
+  </si>
+  <si>
+    <t>TC_1181</t>
   </si>
   <si>
     <t>TC_NAV_001: Main menu navigation</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:52.321Z</t>
-  </si>
-  <si>
-    <t>TC_2321</t>
+    <t>2026-06-23T04:31:01.181Z</t>
+  </si>
+  <si>
+    <t>TC_1183</t>
   </si>
   <si>
     <t>TC_NAV_002: Breadcrumb verification</t>
   </si>
   <si>
-    <t>TC_2322</t>
+    <t>2026-06-23T04:31:01.183Z</t>
+  </si>
+  <si>
+    <t>TC_1184</t>
   </si>
   <si>
     <t>TC_NAV_003: Browser back button navigation</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:52.322Z</t>
+    <t>2026-06-23T04:31:01.184Z</t>
+  </si>
+  <si>
+    <t>TC_1186</t>
   </si>
   <si>
     <t>TC_NAV_004: Browser forward button navigation</t>
   </si>
   <si>
-    <t>TC_2323</t>
+    <t>2026-06-23T04:31:01.186Z</t>
   </si>
   <si>
     <t>TC_NAV_005: Page refresh behavior</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:52.323Z</t>
+    <t>TC_1187</t>
   </si>
   <si>
     <t>TC_NAV_006: External links open in new tab</t>
   </si>
   <si>
-    <t>TC_2324</t>
+    <t>2026-06-23T04:31:01.187Z</t>
   </si>
   <si>
     <t>TC_NAV_007: Internal anchor links navigation</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:52.324Z</t>
+    <t>2026-06-23T04:31:01.188Z</t>
+  </si>
+  <si>
+    <t>TC_1188</t>
   </si>
   <si>
     <t>TC_NAV_008: Sidebar collapse/expand navigation</t>
   </si>
   <si>
-    <t>TC_2325</t>
+    <t>TC_1189</t>
   </si>
   <si>
     <t>TC_NAV_009: Footer links navigation</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:52.325Z</t>
+    <t>2026-06-23T04:31:01.189Z</t>
   </si>
   <si>
     <t>TC_NAV_010: Tab navigation within pages</t>
   </si>
   <si>
-    <t>TC_2326</t>
+    <t>TC_1191</t>
   </si>
   <si>
     <t>TC_SEARCH_001: Basic search functionality</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:52.326Z</t>
-  </si>
-  <si>
-    <t>TC_2327</t>
+    <t>2026-06-23T04:31:01.191Z</t>
   </si>
   <si>
     <t>TC_SEARCH_002: Search with no results</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:52.327Z</t>
+    <t>TC_1192</t>
   </si>
   <si>
     <t>TC_SEARCH_003: Search query persistence</t>
   </si>
   <si>
+    <t>2026-06-23T04:31:01.192Z</t>
+  </si>
+  <si>
+    <t>TC_1193</t>
+  </si>
+  <si>
     <t>TC_SEARCH_004: Apply single filter</t>
   </si>
   <si>
-    <t>TC_2328</t>
+    <t>2026-06-23T04:31:01.193Z</t>
   </si>
   <si>
     <t>TC_SEARCH_005: Apply multiple filters</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:52.328Z</t>
-  </si>
-  <si>
-    <t>TC_2329</t>
+    <t>TC_1195</t>
   </si>
   <si>
     <t>TC_SEARCH_006: Clear all filters</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:52.329Z</t>
+    <t>2026-06-23T04:31:01.195Z</t>
+  </si>
+  <si>
+    <t>TC_1199</t>
   </si>
   <si>
     <t>TC_SEARCH_007: Sort by date ascending</t>
   </si>
   <si>
-    <t>TC_2330</t>
+    <t>2026-06-23T04:31:01.199Z</t>
+  </si>
+  <si>
+    <t>TC_1200</t>
   </si>
   <si>
     <t>TC_SEARCH_008: Sort by date descending</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:52.330Z</t>
+    <t>2026-06-23T04:31:01.200Z</t>
+  </si>
+  <si>
+    <t>TC_1201</t>
   </si>
   <si>
     <t>TC_SEARCH_009: Sort by alphabet</t>
   </si>
   <si>
-    <t>TC_2332</t>
+    <t>2026-06-23T04:31:01.201Z</t>
+  </si>
+  <si>
+    <t>TC_1202</t>
   </si>
   <si>
     <t>TC_SEARCH_010: Search highlighting in results</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:52.332Z</t>
-  </si>
-  <si>
-    <t>TC_8210</t>
+    <t>2026-06-23T04:31:01.202Z</t>
+  </si>
+  <si>
+    <t>TC_4818</t>
   </si>
   <si>
     <t>Deployable Status</t>
@@ -529,64 +574,64 @@
     <t>TC_E2E_001: Complete Student Journey (Register -&gt; Login -&gt; All Modules)</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:38.210Z</t>
-  </si>
-  <si>
-    <t>TC_1422</t>
+    <t>2026-06-23T04:30:44.818Z</t>
+  </si>
+  <si>
+    <t>TC_0097</t>
   </si>
   <si>
     <t>TC_E2E_002: Complete Admin Journey (Register -&gt; Login -&gt; Admin Dashboard)</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:51.422Z</t>
-  </si>
-  <si>
-    <t>TC_2656</t>
+    <t>2026-06-23T04:31:00.097Z</t>
+  </si>
+  <si>
+    <t>TC_1504</t>
   </si>
   <si>
     <t>TC_SMOKE_001: Validate application startup</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:52.656Z</t>
-  </si>
-  <si>
-    <t>TC_3941</t>
+    <t>2026-06-23T04:31:01.504Z</t>
+  </si>
+  <si>
+    <t>TC_2740</t>
   </si>
   <si>
     <t>TC_SMOKE_002: Validate login page accessibility</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.941Z</t>
-  </si>
-  <si>
-    <t>TC_3942</t>
+    <t>2026-06-23T04:31:02.740Z</t>
+  </si>
+  <si>
+    <t>TC_2742</t>
   </si>
   <si>
     <t>TC_SMOKE_003: Validate dashboard access (unauthorized)</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.942Z</t>
-  </si>
-  <si>
-    <t>TC_3944</t>
+    <t>2026-06-23T04:31:02.742Z</t>
+  </si>
+  <si>
+    <t>TC_2744</t>
   </si>
   <si>
     <t>TC_SMOKE_004: Validate primary business flow presence</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.944Z</t>
-  </si>
-  <si>
-    <t>TC_3945</t>
+    <t>2026-06-23T04:31:02.744Z</t>
+  </si>
+  <si>
+    <t>TC_2746</t>
   </si>
   <si>
     <t>TC_SMOKE_005: Validate 404 page for invalid route</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.945Z</t>
-  </si>
-  <si>
-    <t>TC_1423</t>
+    <t>2026-06-23T04:31:02.746Z</t>
+  </si>
+  <si>
+    <t>TC_0098</t>
   </si>
   <si>
     <t>Validation Test</t>
@@ -595,238 +640,256 @@
     <t>TC_ERR_001: Invalid URL routing (404)</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:51.423Z</t>
-  </si>
-  <si>
-    <t>TC_1424</t>
+    <t>2026-06-23T04:31:00.098Z</t>
+  </si>
+  <si>
+    <t>TC_0099</t>
   </si>
   <si>
     <t>TC_ERR_002: Server error rendering (500)</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:51.424Z</t>
-  </si>
-  <si>
-    <t>TC_1425</t>
+    <t>2026-06-23T04:31:00.099Z</t>
   </si>
   <si>
     <t>TC_ERR_003: Network disconnection handling</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:51.425Z</t>
-  </si>
-  <si>
-    <t>TC_1426</t>
+    <t>2026-06-23T04:31:00.100Z</t>
+  </si>
+  <si>
+    <t>TC_0100</t>
   </si>
   <si>
     <t>TC_ERR_004: Graceful degradation on API failure</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:51.426Z</t>
+    <t>TC_0101</t>
   </si>
   <si>
     <t>TC_ERR_005: Form submission timeout handling</t>
   </si>
   <si>
-    <t>TC_1427</t>
+    <t>2026-06-23T04:31:00.101Z</t>
   </si>
   <si>
     <t>TC_ERR_006: Invalid API response format handling</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:51.427Z</t>
+    <t>TC_0102</t>
   </si>
   <si>
     <t>TC_ERR_007: Image loading failure fallback</t>
   </si>
   <si>
-    <t>TC_1429</t>
+    <t>2026-06-23T04:31:00.102Z</t>
+  </si>
+  <si>
+    <t>TC_0103</t>
   </si>
   <si>
     <t>TC_ERR_008: Unauthorized API call handling (401/403)</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:51.429Z</t>
+    <t>2026-06-23T04:31:00.103Z</t>
   </si>
   <si>
     <t>TC_ERR_009: Rate limit exceeded handling (429)</t>
   </si>
   <si>
-    <t>TC_1430</t>
+    <t>TC_0104</t>
   </si>
   <si>
     <t>TC_ERR_010: Error boundary rendering in React/Vite</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:51.430Z</t>
-  </si>
-  <si>
-    <t>TC_1742</t>
+    <t>2026-06-23T04:31:00.104Z</t>
+  </si>
+  <si>
+    <t>TC_0519</t>
   </si>
   <si>
     <t>TC_FORM_001: Required field validation</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:51.742Z</t>
-  </si>
-  <si>
-    <t>TC_1743</t>
+    <t>2026-06-23T04:31:00.519Z</t>
+  </si>
+  <si>
+    <t>TC_0520</t>
   </si>
   <si>
     <t>TC_FORM_002: Invalid email format validation</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:51.743Z</t>
+    <t>2026-06-23T04:31:00.520Z</t>
+  </si>
+  <si>
+    <t>TC_0521</t>
   </si>
   <si>
     <t>TC_FORM_003: Boundary value testing for numbers</t>
   </si>
   <si>
-    <t>TC_1744</t>
+    <t>2026-06-23T04:31:00.521Z</t>
   </si>
   <si>
     <t>TC_FORM_004: Empty field handling on submit</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:51.744Z</t>
-  </si>
-  <si>
-    <t>TC_1745</t>
+    <t>TC_0522</t>
   </si>
   <si>
     <t>TC_FORM_005: Maximum length checks</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:51.745Z</t>
+    <t>2026-06-23T04:31:00.522Z</t>
+  </si>
+  <si>
+    <t>TC_0523</t>
   </si>
   <si>
     <t>TC_FORM_006: Minimum length checks</t>
   </si>
   <si>
-    <t>TC_1746</t>
+    <t>2026-06-23T04:31:00.523Z</t>
   </si>
   <si>
     <t>TC_FORM_007: Numeric only validation</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:51.746Z</t>
+    <t>TC_0524</t>
   </si>
   <si>
     <t>TC_FORM_008: Special character validation rejection</t>
   </si>
   <si>
-    <t>TC_1747</t>
+    <t>2026-06-23T04:31:00.524Z</t>
+  </si>
+  <si>
+    <t>TC_0525</t>
   </si>
   <si>
     <t>TC_FORM_009: Special character validation acceptance</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:51.747Z</t>
-  </si>
-  <si>
-    <t>TC_1749</t>
+    <t>2026-06-23T04:31:00.525Z</t>
+  </si>
+  <si>
+    <t>TC_0526</t>
   </si>
   <si>
     <t>TC_FORM_010: Form reset functionality</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:51.749Z</t>
-  </si>
-  <si>
-    <t>TC_1750</t>
+    <t>2026-06-23T04:31:00.526Z</t>
   </si>
   <si>
     <t>TC_FORM_011: Date picker format validation</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:51.750Z</t>
-  </si>
-  <si>
-    <t>TC_1751</t>
+    <t>TC_0527</t>
   </si>
   <si>
     <t>TC_FORM_012: Future date validation</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:51.751Z</t>
+    <t>2026-06-23T04:31:00.527Z</t>
   </si>
   <si>
     <t>TC_FORM_013: Past date validation</t>
   </si>
   <si>
-    <t>TC_1752</t>
+    <t>TC_0528</t>
   </si>
   <si>
     <t>TC_FORM_014: Dropdown selection validation</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:51.752Z</t>
+    <t>2026-06-23T04:31:00.528Z</t>
+  </si>
+  <si>
+    <t>TC_0532</t>
   </si>
   <si>
     <t>TC_FORM_015: Multi-select dropdown validation</t>
   </si>
   <si>
-    <t>TC_2333</t>
+    <t>2026-06-23T04:31:00.532Z</t>
+  </si>
+  <si>
+    <t>TC_1203</t>
   </si>
   <si>
     <t>TC_SEC_001: Session persistence on reload</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:52.333Z</t>
-  </si>
-  <si>
-    <t>TC_2334</t>
+    <t>2026-06-23T04:31:01.203Z</t>
+  </si>
+  <si>
+    <t>TC_1204</t>
   </si>
   <si>
     <t>TC_SEC_002: Unauthorized access prevention to dashboard</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:52.334Z</t>
+    <t>2026-06-23T04:31:01.204Z</t>
+  </si>
+  <si>
+    <t>TC_1205</t>
   </si>
   <si>
     <t>TC_SEC_003: Protected route redirection to login</t>
   </si>
   <si>
-    <t>TC_2335</t>
+    <t>2026-06-23T04:31:01.205Z</t>
   </si>
   <si>
     <t>TC_SEC_004: Logout invalidates session</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:52.335Z</t>
+    <t>TC_1206</t>
   </si>
   <si>
     <t>TC_SEC_005: Role-based access control (Admin)</t>
   </si>
   <si>
-    <t>TC_2336</t>
+    <t>2026-06-23T04:31:01.206Z</t>
+  </si>
+  <si>
+    <t>TC_1207</t>
   </si>
   <si>
     <t>TC_SEC_006: Role-based access control (User)</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:52.336Z</t>
+    <t>2026-06-23T04:31:01.207Z</t>
   </si>
   <si>
     <t>TC_SEC_007: XSS injection prevention in forms</t>
   </si>
   <si>
-    <t>TC_2337</t>
+    <t>TC_1208</t>
   </si>
   <si>
     <t>TC_SEC_008: SQL injection prevention in search</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:52.337Z</t>
+    <t>2026-06-23T04:31:01.208Z</t>
   </si>
   <si>
     <t>TC_SEC_009: CSRF token presence</t>
   </si>
   <si>
+    <t>TC_1209</t>
+  </si>
+  <si>
     <t>TC_SEC_010: Secure cookie attributes</t>
   </si>
   <si>
-    <t>TC_1741</t>
+    <t>2026-06-23T04:31:01.209Z</t>
+  </si>
+  <si>
+    <t>TC_0518</t>
   </si>
   <si>
     <t>Form Validation Testing</t>
@@ -835,10 +898,10 @@
     <t>should show error for empty form submission</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:51.741Z</t>
-  </si>
-  <si>
-    <t>TC_2319</t>
+    <t>2026-06-23T04:31:00.518Z</t>
+  </si>
+  <si>
+    <t>TC_1177</t>
   </si>
   <si>
     <t>Login &amp; Signup Testing</t>
@@ -847,10 +910,10 @@
     <t>should navigate to login page</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:52.319Z</t>
-  </si>
-  <si>
-    <t>TC_3948</t>
+    <t>2026-06-23T04:31:01.177Z</t>
+  </si>
+  <si>
+    <t>TC_2750</t>
   </si>
   <si>
     <t>UI/UX Test</t>
@@ -859,85 +922,91 @@
     <t>TC_UI_001: Core element visibility on load</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.948Z</t>
-  </si>
-  <si>
-    <t>TC_3950</t>
+    <t>2026-06-23T04:31:02.750Z</t>
+  </si>
+  <si>
+    <t>TC_2752</t>
   </si>
   <si>
     <t>TC_UI_002: Button alignment and spacing</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.950Z</t>
-  </si>
-  <si>
-    <t>TC_3951</t>
+    <t>2026-06-23T04:31:02.752Z</t>
+  </si>
+  <si>
+    <t>TC_2753</t>
   </si>
   <si>
     <t>TC_UI_003: Form layout consistency</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.951Z</t>
-  </si>
-  <si>
-    <t>TC_3953</t>
+    <t>2026-06-23T04:31:02.753Z</t>
+  </si>
+  <si>
+    <t>TC_2755</t>
   </si>
   <si>
     <t>TC_UI_004: Responsive layout checks (Mobile viewport)</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.953Z</t>
-  </si>
-  <si>
-    <t>TC_3954</t>
+    <t>2026-06-23T04:31:02.755Z</t>
+  </si>
+  <si>
+    <t>TC_2756</t>
   </si>
   <si>
     <t>TC_UI_005: Responsive layout checks (Tablet viewport)</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.954Z</t>
-  </si>
-  <si>
-    <t>TC_3955</t>
+    <t>2026-06-23T04:31:02.756Z</t>
+  </si>
+  <si>
+    <t>TC_2757</t>
   </si>
   <si>
     <t>TC_UI_006: Navigation menu usability</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.955Z</t>
+    <t>2026-06-23T04:31:02.757Z</t>
+  </si>
+  <si>
+    <t>TC_2759</t>
   </si>
   <si>
     <t>TC_UI_007: Broken link detection across major pages</t>
   </si>
   <si>
-    <t>TC_3956</t>
+    <t>2026-06-23T04:31:02.759Z</t>
+  </si>
+  <si>
+    <t>TC_2760</t>
   </si>
   <si>
     <t>TC_UI_008: Image loading and resolution verification</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.956Z</t>
-  </si>
-  <si>
-    <t>TC_3957</t>
+    <t>2026-06-23T04:31:02.760Z</t>
+  </si>
+  <si>
+    <t>TC_2761</t>
   </si>
   <si>
     <t>TC_UI_009: Font family and typography consistency</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.957Z</t>
-  </si>
-  <si>
-    <t>TC_3958</t>
+    <t>2026-06-23T04:31:02.762Z</t>
+  </si>
+  <si>
+    <t>TC_2765</t>
   </si>
   <si>
     <t>TC_UI_010: Color palette and contrast accessibility</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.958Z</t>
-  </si>
-  <si>
-    <t>TC_3959</t>
+    <t>2026-06-23T04:31:02.765Z</t>
+  </si>
+  <si>
+    <t>TC_2768</t>
   </si>
   <si>
     <t>Unit Testing</t>
@@ -946,118 +1015,121 @@
     <t>TC_UNIT_001: Validate password hashing utility logic</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.959Z</t>
-  </si>
-  <si>
-    <t>TC_3960</t>
+    <t>2026-06-23T04:31:02.768Z</t>
+  </si>
+  <si>
+    <t>TC_2770</t>
   </si>
   <si>
     <t>TC_UNIT_002: Validate email regex format utility</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.960Z</t>
-  </si>
-  <si>
-    <t>TC_3962</t>
+    <t>2026-06-23T04:31:02.770Z</t>
+  </si>
+  <si>
+    <t>TC_2771</t>
   </si>
   <si>
     <t>TC_UNIT_003: Validate URL parsing utility</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.962Z</t>
-  </si>
-  <si>
-    <t>TC_3963</t>
+    <t>2026-06-23T04:31:02.771Z</t>
+  </si>
+  <si>
+    <t>TC_2772</t>
   </si>
   <si>
     <t>TC_UNIT_004: Validate date formatting helper</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.963Z</t>
-  </si>
-  <si>
-    <t>TC_3964</t>
+    <t>2026-06-23T04:31:02.772Z</t>
+  </si>
+  <si>
+    <t>TC_2773</t>
   </si>
   <si>
     <t>TC_UNIT_005: Verify number currency formatting helper</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.964Z</t>
-  </si>
-  <si>
-    <t>TC_3966</t>
+    <t>2026-06-23T04:31:02.773Z</t>
+  </si>
+  <si>
+    <t>TC_2774</t>
   </si>
   <si>
     <t>TC_UNIT_006: Check application state reducer for login</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.966Z</t>
+    <t>2026-06-23T04:31:02.774Z</t>
+  </si>
+  <si>
+    <t>TC_2775</t>
   </si>
   <si>
     <t>TC_UNIT_007: Check application state reducer for logout</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.967Z</t>
-  </si>
-  <si>
-    <t>TC_3968</t>
+    <t>2026-06-23T04:31:02.775Z</t>
+  </si>
+  <si>
+    <t>TC_2782</t>
   </si>
   <si>
     <t>TC_UNIT_008: Validate local storage persistence helper</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.968Z</t>
+    <t>2026-06-23T04:31:02.782Z</t>
+  </si>
+  <si>
+    <t>TC_2783</t>
   </si>
   <si>
     <t>TC_UNIT_009: Test mock data generation for dashboard</t>
   </si>
   <si>
-    <t>TC_3969</t>
+    <t>2026-06-23T04:31:02.783Z</t>
   </si>
   <si>
     <t>TC_UNIT_010: Validate theme toggler state boolean logic</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.969Z</t>
-  </si>
-  <si>
-    <t>TC_3970</t>
+    <t>TC_2784</t>
   </si>
   <si>
     <t>TC_UNIT_011: Test array sorting utility for company list</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.970Z</t>
-  </si>
-  <si>
-    <t>TC_3971</t>
+    <t>2026-06-23T04:31:02.784Z</t>
+  </si>
+  <si>
+    <t>TC_2785</t>
   </si>
   <si>
     <t>TC_UNIT_012: Test pagination offset calculation utility</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.971Z</t>
-  </si>
-  <si>
-    <t>TC_3972</t>
+    <t>2026-06-23T04:31:02.785Z</t>
+  </si>
+  <si>
+    <t>TC_2786</t>
   </si>
   <si>
     <t>TC_UNIT_013: Verify input sanitization helper (XSS prevention)</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.972Z</t>
+    <t>2026-06-23T04:31:02.786Z</t>
   </si>
   <si>
     <t>TC_UNIT_014: Check token decoding function for expiration logic</t>
   </si>
   <si>
-    <t>TC_3973</t>
+    <t>TC_2787</t>
   </si>
   <si>
     <t>TC_UNIT_015: Validate component classNames concatenation utility</t>
   </si>
   <si>
-    <t>2026-06-18T06:05:53.973Z</t>
+    <t>2026-06-23T04:31:02.787Z</t>
   </si>
 </sst>
 </file>
@@ -1520,7 +1592,7 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>124075</v>
+        <v>108823</v>
       </c>
       <c r="I2" t="s">
         <v>18</v>
@@ -1555,7 +1627,7 @@
         <v>17</v>
       </c>
       <c r="H3">
-        <v>198094</v>
+        <v>241551</v>
       </c>
       <c r="I3" t="s">
         <v>23</v>
@@ -1569,13 +1641,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -1590,10 +1662,10 @@
         <v>17</v>
       </c>
       <c r="H4">
-        <v>107976</v>
+        <v>230031</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -1604,13 +1676,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -1625,10 +1697,10 @@
         <v>17</v>
       </c>
       <c r="H5">
-        <v>258982</v>
+        <v>178355</v>
       </c>
       <c r="I5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
@@ -1639,13 +1711,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -1660,10 +1732,10 @@
         <v>17</v>
       </c>
       <c r="H6">
-        <v>128694</v>
+        <v>141546</v>
       </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -1674,13 +1746,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -1695,10 +1767,10 @@
         <v>17</v>
       </c>
       <c r="H7">
-        <v>204637</v>
+        <v>180793</v>
       </c>
       <c r="I7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -1709,13 +1781,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -1730,10 +1802,10 @@
         <v>17</v>
       </c>
       <c r="H8">
-        <v>144033</v>
+        <v>236228</v>
       </c>
       <c r="I8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -1744,31 +1816,31 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9">
+        <v>239602</v>
+      </c>
+      <c r="I9" t="s">
         <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9">
-        <v>65301</v>
-      </c>
-      <c r="I9" t="s">
-        <v>38</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
@@ -1800,7 +1872,7 @@
         <v>17</v>
       </c>
       <c r="H10">
-        <v>244498</v>
+        <v>184035</v>
       </c>
       <c r="I10" t="s">
         <v>42</v>
@@ -1835,7 +1907,7 @@
         <v>17</v>
       </c>
       <c r="H11">
-        <v>205946</v>
+        <v>173693</v>
       </c>
       <c r="I11" t="s">
         <v>45</v>
@@ -1870,7 +1942,7 @@
         <v>17</v>
       </c>
       <c r="H12">
-        <v>176629</v>
+        <v>89844</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -1905,7 +1977,7 @@
         <v>17</v>
       </c>
       <c r="H13">
-        <v>216772</v>
+        <v>294235</v>
       </c>
       <c r="I13" t="s">
         <v>48</v>
@@ -1940,7 +2012,7 @@
         <v>17</v>
       </c>
       <c r="H14">
-        <v>206446</v>
+        <v>252169</v>
       </c>
       <c r="I14" t="s">
         <v>52</v>
@@ -1954,13 +2026,13 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -1975,10 +2047,10 @@
         <v>17</v>
       </c>
       <c r="H15">
-        <v>74450</v>
+        <v>174483</v>
       </c>
       <c r="I15" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J15" t="s">
         <v>19</v>
@@ -1989,31 +2061,31 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
       </c>
       <c r="C16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16">
+        <v>285393</v>
+      </c>
+      <c r="I16" t="s">
         <v>55</v>
-      </c>
-      <c r="D16" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16">
-        <v>132164</v>
-      </c>
-      <c r="I16" t="s">
-        <v>56</v>
       </c>
       <c r="J16" t="s">
         <v>19</v>
@@ -2024,13 +2096,13 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
         <v>14</v>
@@ -2045,10 +2117,10 @@
         <v>17</v>
       </c>
       <c r="H17">
-        <v>228879</v>
+        <v>233646</v>
       </c>
       <c r="I17" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J17" t="s">
         <v>19</v>
@@ -2059,31 +2131,31 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
       </c>
       <c r="C18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18">
+        <v>286410</v>
+      </c>
+      <c r="I18" t="s">
         <v>59</v>
-      </c>
-      <c r="D18" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18">
-        <v>101673</v>
-      </c>
-      <c r="I18" t="s">
-        <v>60</v>
       </c>
       <c r="J18" t="s">
         <v>19</v>
@@ -2094,13 +2166,13 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
@@ -2115,10 +2187,10 @@
         <v>17</v>
       </c>
       <c r="H19">
-        <v>201736</v>
+        <v>146077</v>
       </c>
       <c r="I19" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J19" t="s">
         <v>19</v>
@@ -2129,31 +2201,31 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
       </c>
       <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20">
+        <v>188180</v>
+      </c>
+      <c r="I20" t="s">
         <v>63</v>
-      </c>
-      <c r="D20" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20">
-        <v>96318</v>
-      </c>
-      <c r="I20" t="s">
-        <v>64</v>
       </c>
       <c r="J20" t="s">
         <v>19</v>
@@ -2164,13 +2236,13 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
@@ -2185,10 +2257,10 @@
         <v>17</v>
       </c>
       <c r="H21">
-        <v>149869</v>
+        <v>240850</v>
       </c>
       <c r="I21" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J21" t="s">
         <v>19</v>
@@ -2199,31 +2271,31 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
         <v>12</v>
       </c>
       <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22">
+        <v>108711</v>
+      </c>
+      <c r="I22" t="s">
         <v>67</v>
-      </c>
-      <c r="D22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22">
-        <v>266254</v>
-      </c>
-      <c r="I22" t="s">
-        <v>68</v>
       </c>
       <c r="J22" t="s">
         <v>19</v>
@@ -2234,13 +2306,13 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D23" t="s">
         <v>14</v>
@@ -2255,10 +2327,10 @@
         <v>17</v>
       </c>
       <c r="H23">
-        <v>281538</v>
+        <v>132023</v>
       </c>
       <c r="I23" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J23" t="s">
         <v>19</v>
@@ -2269,31 +2341,31 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
       </c>
       <c r="C24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24">
+        <v>99445</v>
+      </c>
+      <c r="I24" t="s">
         <v>71</v>
-      </c>
-      <c r="D24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H24">
-        <v>251969</v>
-      </c>
-      <c r="I24" t="s">
-        <v>72</v>
       </c>
       <c r="J24" t="s">
         <v>19</v>
@@ -2304,13 +2376,13 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D25" t="s">
         <v>14</v>
@@ -2325,10 +2397,10 @@
         <v>17</v>
       </c>
       <c r="H25">
-        <v>296048</v>
+        <v>129420</v>
       </c>
       <c r="I25" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J25" t="s">
         <v>19</v>
@@ -2339,31 +2411,31 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
       </c>
       <c r="C26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26">
+        <v>278851</v>
+      </c>
+      <c r="I26" t="s">
         <v>75</v>
-      </c>
-      <c r="D26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H26">
-        <v>137604</v>
-      </c>
-      <c r="I26" t="s">
-        <v>76</v>
       </c>
       <c r="J26" t="s">
         <v>19</v>
@@ -2374,13 +2446,13 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B27" t="s">
         <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
         <v>14</v>
@@ -2395,10 +2467,10 @@
         <v>17</v>
       </c>
       <c r="H27">
-        <v>132565</v>
+        <v>273023</v>
       </c>
       <c r="I27" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J27" t="s">
         <v>19</v>
@@ -2409,31 +2481,31 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B28" t="s">
         <v>12</v>
       </c>
       <c r="C28" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28">
+        <v>155909</v>
+      </c>
+      <c r="I28" t="s">
         <v>79</v>
-      </c>
-      <c r="D28" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" t="s">
-        <v>15</v>
-      </c>
-      <c r="F28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H28">
-        <v>70921</v>
-      </c>
-      <c r="I28" t="s">
-        <v>80</v>
       </c>
       <c r="J28" t="s">
         <v>19</v>
@@ -2444,13 +2516,13 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D29" t="s">
         <v>14</v>
@@ -2465,10 +2537,10 @@
         <v>17</v>
       </c>
       <c r="H29">
-        <v>170631</v>
+        <v>103774</v>
       </c>
       <c r="I29" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J29" t="s">
         <v>19</v>
@@ -2479,13 +2551,13 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
@@ -2500,10 +2572,10 @@
         <v>17</v>
       </c>
       <c r="H30">
-        <v>145591</v>
+        <v>84197</v>
       </c>
       <c r="I30" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J30" t="s">
         <v>19</v>
@@ -2514,13 +2586,13 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D31" t="s">
         <v>14</v>
@@ -2535,10 +2607,10 @@
         <v>17</v>
       </c>
       <c r="H31">
-        <v>174756</v>
+        <v>86719</v>
       </c>
       <c r="I31" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J31" t="s">
         <v>19</v>
@@ -2549,13 +2621,13 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
         <v>14</v>
@@ -2570,10 +2642,10 @@
         <v>17</v>
       </c>
       <c r="H32">
-        <v>152736</v>
+        <v>215848</v>
       </c>
       <c r="I32" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J32" t="s">
         <v>19</v>
@@ -2584,13 +2656,13 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D33" t="s">
         <v>14</v>
@@ -2605,10 +2677,10 @@
         <v>17</v>
       </c>
       <c r="H33">
-        <v>264004</v>
+        <v>212172</v>
       </c>
       <c r="I33" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J33" t="s">
         <v>19</v>
@@ -2619,13 +2691,13 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
         <v>14</v>
@@ -2640,10 +2712,10 @@
         <v>17</v>
       </c>
       <c r="H34">
-        <v>223589</v>
+        <v>264445</v>
       </c>
       <c r="I34" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J34" t="s">
         <v>19</v>
@@ -2654,13 +2726,13 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
         <v>14</v>
@@ -2675,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="H35">
-        <v>285020</v>
+        <v>173670</v>
       </c>
       <c r="I35" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J35" t="s">
         <v>19</v>
@@ -2689,13 +2761,13 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D36" t="s">
         <v>14</v>
@@ -2710,10 +2782,10 @@
         <v>17</v>
       </c>
       <c r="H36">
-        <v>110014</v>
+        <v>294531</v>
       </c>
       <c r="I36" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J36" t="s">
         <v>19</v>
@@ -2724,13 +2796,13 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B37" t="s">
         <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D37" t="s">
         <v>14</v>
@@ -2745,10 +2817,10 @@
         <v>17</v>
       </c>
       <c r="H37">
-        <v>190440</v>
+        <v>196373</v>
       </c>
       <c r="I37" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="J37" t="s">
         <v>19</v>
@@ -2759,13 +2831,13 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D38" t="s">
         <v>14</v>
@@ -2780,10 +2852,10 @@
         <v>17</v>
       </c>
       <c r="H38">
-        <v>120599</v>
+        <v>162713</v>
       </c>
       <c r="I38" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="J38" t="s">
         <v>19</v>
@@ -2794,13 +2866,13 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D39" t="s">
         <v>14</v>
@@ -2815,10 +2887,10 @@
         <v>17</v>
       </c>
       <c r="H39">
-        <v>290455</v>
+        <v>196993</v>
       </c>
       <c r="I39" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="J39" t="s">
         <v>19</v>
@@ -2829,13 +2901,13 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="D40" t="s">
         <v>14</v>
@@ -2850,10 +2922,10 @@
         <v>17</v>
       </c>
       <c r="H40">
-        <v>248564</v>
+        <v>189687</v>
       </c>
       <c r="I40" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J40" t="s">
         <v>19</v>
@@ -2864,13 +2936,13 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B41" t="s">
         <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D41" t="s">
         <v>14</v>
@@ -2885,10 +2957,10 @@
         <v>17</v>
       </c>
       <c r="H41">
-        <v>234156</v>
+        <v>67048</v>
       </c>
       <c r="I41" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="J41" t="s">
         <v>19</v>
@@ -2899,13 +2971,13 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
         <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D42" t="s">
         <v>14</v>
@@ -2920,10 +2992,10 @@
         <v>17</v>
       </c>
       <c r="H42">
-        <v>264241</v>
+        <v>238757</v>
       </c>
       <c r="I42" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="J42" t="s">
         <v>19</v>
@@ -2934,13 +3006,13 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B43" t="s">
         <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D43" t="s">
         <v>14</v>
@@ -2955,10 +3027,10 @@
         <v>17</v>
       </c>
       <c r="H43">
-        <v>183080</v>
+        <v>167910</v>
       </c>
       <c r="I43" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="J43" t="s">
         <v>19</v>
@@ -2969,13 +3041,13 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B44" t="s">
         <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D44" t="s">
         <v>14</v>
@@ -2990,10 +3062,10 @@
         <v>17</v>
       </c>
       <c r="H44">
-        <v>165714</v>
+        <v>143842</v>
       </c>
       <c r="I44" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J44" t="s">
         <v>19</v>
@@ -3004,13 +3076,13 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D45" t="s">
         <v>14</v>
@@ -3025,10 +3097,10 @@
         <v>17</v>
       </c>
       <c r="H45">
-        <v>260425</v>
+        <v>232028</v>
       </c>
       <c r="I45" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="J45" t="s">
         <v>19</v>
@@ -3039,13 +3111,13 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D46" t="s">
         <v>14</v>
@@ -3060,10 +3132,10 @@
         <v>17</v>
       </c>
       <c r="H46">
-        <v>73424</v>
+        <v>103255</v>
       </c>
       <c r="I46" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="J46" t="s">
         <v>19</v>
@@ -3074,13 +3146,13 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B47" t="s">
         <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D47" t="s">
         <v>14</v>
@@ -3095,10 +3167,10 @@
         <v>17</v>
       </c>
       <c r="H47">
-        <v>123130</v>
+        <v>226564</v>
       </c>
       <c r="I47" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="J47" t="s">
         <v>19</v>
@@ -3109,13 +3181,13 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D48" t="s">
         <v>14</v>
@@ -3130,10 +3202,10 @@
         <v>17</v>
       </c>
       <c r="H48">
-        <v>94680</v>
+        <v>219766</v>
       </c>
       <c r="I48" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="J48" t="s">
         <v>19</v>
@@ -3144,13 +3216,13 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D49" t="s">
         <v>14</v>
@@ -3165,10 +3237,10 @@
         <v>17</v>
       </c>
       <c r="H49">
-        <v>138153</v>
+        <v>275731</v>
       </c>
       <c r="I49" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="J49" t="s">
         <v>19</v>
@@ -3179,13 +3251,13 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B50" t="s">
         <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D50" t="s">
         <v>14</v>
@@ -3200,10 +3272,10 @@
         <v>17</v>
       </c>
       <c r="H50">
-        <v>140666</v>
+        <v>211702</v>
       </c>
       <c r="I50" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="J50" t="s">
         <v>19</v>
@@ -3214,13 +3286,13 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D51" t="s">
         <v>14</v>
@@ -3235,10 +3307,10 @@
         <v>17</v>
       </c>
       <c r="H51">
-        <v>260486</v>
+        <v>126091</v>
       </c>
       <c r="I51" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="J51" t="s">
         <v>19</v>
@@ -3249,13 +3321,13 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B52" t="s">
         <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D52" t="s">
         <v>14</v>
@@ -3270,10 +3342,10 @@
         <v>17</v>
       </c>
       <c r="H52">
-        <v>174607</v>
+        <v>139702</v>
       </c>
       <c r="I52" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="J52" t="s">
         <v>19</v>
@@ -3284,13 +3356,13 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B53" t="s">
         <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="D53" t="s">
         <v>14</v>
@@ -3305,10 +3377,10 @@
         <v>17</v>
       </c>
       <c r="H53">
-        <v>294408</v>
+        <v>123208</v>
       </c>
       <c r="I53" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J53" t="s">
         <v>19</v>
@@ -3319,13 +3391,13 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="D54" t="s">
         <v>14</v>
@@ -3340,10 +3412,10 @@
         <v>17</v>
       </c>
       <c r="H54">
-        <v>202936</v>
+        <v>100365</v>
       </c>
       <c r="I54" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="J54" t="s">
         <v>19</v>
@@ -3354,13 +3426,13 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D55" t="s">
         <v>14</v>
@@ -3375,10 +3447,10 @@
         <v>17</v>
       </c>
       <c r="H55">
-        <v>206934</v>
+        <v>196078</v>
       </c>
       <c r="I55" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="J55" t="s">
         <v>19</v>
@@ -3389,13 +3461,13 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B56" t="s">
         <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="D56" t="s">
         <v>14</v>
@@ -3410,10 +3482,10 @@
         <v>17</v>
       </c>
       <c r="H56">
-        <v>125089</v>
+        <v>236986</v>
       </c>
       <c r="I56" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="J56" t="s">
         <v>19</v>
@@ -3424,13 +3496,13 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B57" t="s">
         <v>12</v>
       </c>
       <c r="C57" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D57" t="s">
         <v>14</v>
@@ -3445,10 +3517,10 @@
         <v>17</v>
       </c>
       <c r="H57">
-        <v>188850</v>
+        <v>103760</v>
       </c>
       <c r="I57" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="J57" t="s">
         <v>19</v>
@@ -3459,13 +3531,13 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
       </c>
       <c r="C58" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="D58" t="s">
         <v>14</v>
@@ -3480,10 +3552,10 @@
         <v>17</v>
       </c>
       <c r="H58">
-        <v>251604</v>
+        <v>180620</v>
       </c>
       <c r="I58" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="J58" t="s">
         <v>19</v>
@@ -3494,13 +3566,13 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B59" t="s">
         <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="D59" t="s">
         <v>14</v>
@@ -3515,10 +3587,10 @@
         <v>17</v>
       </c>
       <c r="H59">
-        <v>278435</v>
+        <v>255877</v>
       </c>
       <c r="I59" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="J59" t="s">
         <v>19</v>
@@ -3529,13 +3601,13 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B60" t="s">
         <v>12</v>
       </c>
       <c r="C60" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D60" t="s">
         <v>14</v>
@@ -3550,10 +3622,10 @@
         <v>17</v>
       </c>
       <c r="H60">
-        <v>160016</v>
+        <v>120395</v>
       </c>
       <c r="I60" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="J60" t="s">
         <v>19</v>
@@ -3564,13 +3636,13 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B61" t="s">
         <v>12</v>
       </c>
       <c r="C61" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D61" t="s">
         <v>14</v>
@@ -3585,10 +3657,10 @@
         <v>17</v>
       </c>
       <c r="H61">
-        <v>166012</v>
+        <v>92224</v>
       </c>
       <c r="I61" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="J61" t="s">
         <v>19</v>
@@ -3599,13 +3671,13 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="B62" t="s">
         <v>12</v>
       </c>
       <c r="C62" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="D62" t="s">
         <v>14</v>
@@ -3620,10 +3692,10 @@
         <v>17</v>
       </c>
       <c r="H62">
-        <v>137872</v>
+        <v>288480</v>
       </c>
       <c r="I62" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="J62" t="s">
         <v>19</v>
@@ -3634,13 +3706,13 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="B63" t="s">
         <v>12</v>
       </c>
       <c r="C63" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="D63" t="s">
         <v>14</v>
@@ -3655,10 +3727,10 @@
         <v>17</v>
       </c>
       <c r="H63">
-        <v>246983</v>
+        <v>224525</v>
       </c>
       <c r="I63" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="J63" t="s">
         <v>19</v>
@@ -3669,13 +3741,13 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B64" t="s">
         <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="D64" t="s">
         <v>14</v>
@@ -3690,10 +3762,10 @@
         <v>17</v>
       </c>
       <c r="H64">
-        <v>288728</v>
+        <v>237540</v>
       </c>
       <c r="I64" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="J64" t="s">
         <v>19</v>
@@ -3704,13 +3776,13 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="B65" t="s">
         <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="D65" t="s">
         <v>14</v>
@@ -3725,10 +3797,10 @@
         <v>17</v>
       </c>
       <c r="H65">
-        <v>213818</v>
+        <v>135072</v>
       </c>
       <c r="I65" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="J65" t="s">
         <v>19</v>
@@ -3739,13 +3811,13 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="B66" t="s">
         <v>12</v>
       </c>
       <c r="C66" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="D66" t="s">
         <v>14</v>
@@ -3760,10 +3832,10 @@
         <v>17</v>
       </c>
       <c r="H66">
-        <v>73150</v>
+        <v>212607</v>
       </c>
       <c r="I66" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="J66" t="s">
         <v>19</v>
@@ -3774,13 +3846,13 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="B67" t="s">
         <v>12</v>
       </c>
       <c r="C67" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="D67" t="s">
         <v>14</v>
@@ -3795,10 +3867,10 @@
         <v>17</v>
       </c>
       <c r="H67">
-        <v>282598</v>
+        <v>145997</v>
       </c>
       <c r="I67" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="J67" t="s">
         <v>19</v>
@@ -3809,13 +3881,13 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="B68" t="s">
         <v>12</v>
       </c>
       <c r="C68" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D68" t="s">
         <v>14</v>
@@ -3830,10 +3902,10 @@
         <v>17</v>
       </c>
       <c r="H68">
-        <v>239909</v>
+        <v>88122</v>
       </c>
       <c r="I68" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="J68" t="s">
         <v>19</v>
@@ -3844,13 +3916,13 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="B69" t="s">
         <v>12</v>
       </c>
       <c r="C69" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="D69" t="s">
         <v>14</v>
@@ -3865,10 +3937,10 @@
         <v>17</v>
       </c>
       <c r="H69">
-        <v>98017</v>
+        <v>148052</v>
       </c>
       <c r="I69" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="J69" t="s">
         <v>19</v>
@@ -3937,13 +4009,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="B2" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -3958,10 +4030,10 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>231308</v>
+        <v>121373</v>
       </c>
       <c r="I2" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -3972,13 +4044,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B3" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="C3" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -3993,10 +4065,10 @@
         <v>17</v>
       </c>
       <c r="H3">
-        <v>126094</v>
+        <v>253698</v>
       </c>
       <c r="I3" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -4007,13 +4079,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="C4" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -4028,10 +4100,10 @@
         <v>17</v>
       </c>
       <c r="H4">
-        <v>129188</v>
+        <v>132266</v>
       </c>
       <c r="I4" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -4042,13 +4114,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="C5" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -4063,10 +4135,10 @@
         <v>17</v>
       </c>
       <c r="H5">
-        <v>252944</v>
+        <v>172317</v>
       </c>
       <c r="I5" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
@@ -4077,13 +4149,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="B6" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="C6" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -4098,10 +4170,10 @@
         <v>17</v>
       </c>
       <c r="H6">
-        <v>275003</v>
+        <v>269422</v>
       </c>
       <c r="I6" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -4112,13 +4184,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" t="s">
         <v>183</v>
       </c>
-      <c r="B7" t="s">
-        <v>168</v>
-      </c>
       <c r="C7" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -4133,10 +4205,10 @@
         <v>17</v>
       </c>
       <c r="H7">
-        <v>98345</v>
+        <v>159075</v>
       </c>
       <c r="I7" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -4147,13 +4219,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="B8" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="C8" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -4168,10 +4240,10 @@
         <v>17</v>
       </c>
       <c r="H8">
-        <v>208081</v>
+        <v>238818</v>
       </c>
       <c r="I8" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -4240,13 +4312,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C2" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -4261,10 +4333,10 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>224154</v>
+        <v>109851</v>
       </c>
       <c r="I2" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -4275,13 +4347,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="B3" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C3" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -4296,10 +4368,10 @@
         <v>17</v>
       </c>
       <c r="H3">
-        <v>203022</v>
+        <v>96590</v>
       </c>
       <c r="I3" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -4310,13 +4382,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C4" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -4331,10 +4403,10 @@
         <v>17</v>
       </c>
       <c r="H4">
-        <v>250813</v>
+        <v>264583</v>
       </c>
       <c r="I4" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -4345,13 +4417,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="B5" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C5" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -4366,10 +4438,10 @@
         <v>17</v>
       </c>
       <c r="H5">
-        <v>125925</v>
+        <v>151738</v>
       </c>
       <c r="I5" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
@@ -4380,13 +4452,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="B6" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C6" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -4401,10 +4473,10 @@
         <v>17</v>
       </c>
       <c r="H6">
-        <v>103276</v>
+        <v>242115</v>
       </c>
       <c r="I6" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -4415,13 +4487,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="B7" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C7" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -4436,10 +4508,10 @@
         <v>17</v>
       </c>
       <c r="H7">
-        <v>138907</v>
+        <v>277810</v>
       </c>
       <c r="I7" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -4450,13 +4522,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C8" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -4471,10 +4543,10 @@
         <v>17</v>
       </c>
       <c r="H8">
-        <v>237037</v>
+        <v>130513</v>
       </c>
       <c r="I8" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -4485,13 +4557,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="B9" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C9" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -4506,10 +4578,10 @@
         <v>17</v>
       </c>
       <c r="H9">
-        <v>123430</v>
+        <v>272657</v>
       </c>
       <c r="I9" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
@@ -4520,13 +4592,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="B10" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C10" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -4541,10 +4613,10 @@
         <v>17</v>
       </c>
       <c r="H10">
-        <v>93835</v>
+        <v>171160</v>
       </c>
       <c r="I10" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="J10" t="s">
         <v>19</v>
@@ -4555,13 +4627,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="B11" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C11" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -4576,10 +4648,10 @@
         <v>17</v>
       </c>
       <c r="H11">
-        <v>219373</v>
+        <v>112080</v>
       </c>
       <c r="I11" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="J11" t="s">
         <v>19</v>
@@ -4590,13 +4662,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="B12" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C12" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
@@ -4611,10 +4683,10 @@
         <v>17</v>
       </c>
       <c r="H12">
-        <v>159451</v>
+        <v>111217</v>
       </c>
       <c r="I12" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="J12" t="s">
         <v>19</v>
@@ -4625,13 +4697,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="B13" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C13" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -4646,10 +4718,10 @@
         <v>17</v>
       </c>
       <c r="H13">
-        <v>269017</v>
+        <v>106077</v>
       </c>
       <c r="I13" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="J13" t="s">
         <v>19</v>
@@ -4660,13 +4732,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="B14" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C14" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="D14" t="s">
         <v>14</v>
@@ -4681,10 +4753,10 @@
         <v>17</v>
       </c>
       <c r="H14">
-        <v>127490</v>
+        <v>122951</v>
       </c>
       <c r="I14" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="J14" t="s">
         <v>19</v>
@@ -4695,13 +4767,13 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="B15" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C15" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -4716,10 +4788,10 @@
         <v>17</v>
       </c>
       <c r="H15">
-        <v>256749</v>
+        <v>77260</v>
       </c>
       <c r="I15" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="J15" t="s">
         <v>19</v>
@@ -4730,13 +4802,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="B16" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C16" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="D16" t="s">
         <v>14</v>
@@ -4751,10 +4823,10 @@
         <v>17</v>
       </c>
       <c r="H16">
-        <v>292489</v>
+        <v>233456</v>
       </c>
       <c r="I16" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="J16" t="s">
         <v>19</v>
@@ -4765,13 +4837,13 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="B17" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C17" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="D17" t="s">
         <v>14</v>
@@ -4786,10 +4858,10 @@
         <v>17</v>
       </c>
       <c r="H17">
-        <v>121936</v>
+        <v>78271</v>
       </c>
       <c r="I17" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="J17" t="s">
         <v>19</v>
@@ -4800,13 +4872,13 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="B18" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C18" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="D18" t="s">
         <v>14</v>
@@ -4821,10 +4893,10 @@
         <v>17</v>
       </c>
       <c r="H18">
-        <v>111415</v>
+        <v>239137</v>
       </c>
       <c r="I18" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="J18" t="s">
         <v>19</v>
@@ -4835,13 +4907,13 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="B19" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C19" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
@@ -4856,10 +4928,10 @@
         <v>17</v>
       </c>
       <c r="H19">
-        <v>296766</v>
+        <v>236080</v>
       </c>
       <c r="I19" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="J19" t="s">
         <v>19</v>
@@ -4870,13 +4942,13 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="B20" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C20" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
@@ -4891,10 +4963,10 @@
         <v>17</v>
       </c>
       <c r="H20">
-        <v>205372</v>
+        <v>198806</v>
       </c>
       <c r="I20" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="J20" t="s">
         <v>19</v>
@@ -4905,13 +4977,13 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="B21" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C21" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
@@ -4926,10 +4998,10 @@
         <v>17</v>
       </c>
       <c r="H21">
-        <v>298877</v>
+        <v>94130</v>
       </c>
       <c r="I21" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="J21" t="s">
         <v>19</v>
@@ -4940,13 +5012,13 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="B22" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C22" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="D22" t="s">
         <v>14</v>
@@ -4961,10 +5033,10 @@
         <v>17</v>
       </c>
       <c r="H22">
-        <v>200262</v>
+        <v>237855</v>
       </c>
       <c r="I22" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="J22" t="s">
         <v>19</v>
@@ -4975,13 +5047,13 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="B23" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C23" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="D23" t="s">
         <v>14</v>
@@ -4996,10 +5068,10 @@
         <v>17</v>
       </c>
       <c r="H23">
-        <v>278277</v>
+        <v>140380</v>
       </c>
       <c r="I23" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="J23" t="s">
         <v>19</v>
@@ -5010,13 +5082,13 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="B24" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C24" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
         <v>14</v>
@@ -5031,10 +5103,10 @@
         <v>17</v>
       </c>
       <c r="H24">
-        <v>79846</v>
+        <v>74009</v>
       </c>
       <c r="I24" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="J24" t="s">
         <v>19</v>
@@ -5045,13 +5117,13 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="B25" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C25" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>14</v>
@@ -5066,10 +5138,10 @@
         <v>17</v>
       </c>
       <c r="H25">
-        <v>269987</v>
+        <v>94340</v>
       </c>
       <c r="I25" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="J25" t="s">
         <v>19</v>
@@ -5080,13 +5152,13 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C26" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="D26" t="s">
         <v>14</v>
@@ -5101,10 +5173,10 @@
         <v>17</v>
       </c>
       <c r="H26">
-        <v>235616</v>
+        <v>72979</v>
       </c>
       <c r="I26" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="J26" t="s">
         <v>19</v>
@@ -5115,13 +5187,13 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C27" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="D27" t="s">
         <v>14</v>
@@ -5136,10 +5208,10 @@
         <v>17</v>
       </c>
       <c r="H27">
-        <v>140452</v>
+        <v>81746</v>
       </c>
       <c r="I27" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="J27" t="s">
         <v>19</v>
@@ -5150,13 +5222,13 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C28" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="D28" t="s">
         <v>14</v>
@@ -5171,10 +5243,10 @@
         <v>17</v>
       </c>
       <c r="H28">
-        <v>110126</v>
+        <v>64093</v>
       </c>
       <c r="I28" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="J28" t="s">
         <v>19</v>
@@ -5185,13 +5257,13 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C29" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="D29" t="s">
         <v>14</v>
@@ -5206,10 +5278,10 @@
         <v>17</v>
       </c>
       <c r="H29">
-        <v>124024</v>
+        <v>84815</v>
       </c>
       <c r="I29" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="J29" t="s">
         <v>19</v>
@@ -5220,13 +5292,13 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C30" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
@@ -5241,10 +5313,10 @@
         <v>17</v>
       </c>
       <c r="H30">
-        <v>168225</v>
+        <v>126402</v>
       </c>
       <c r="I30" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="J30" t="s">
         <v>19</v>
@@ -5255,13 +5327,13 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="B31" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="D31" t="s">
         <v>14</v>
@@ -5276,10 +5348,10 @@
         <v>17</v>
       </c>
       <c r="H31">
-        <v>104368</v>
+        <v>200855</v>
       </c>
       <c r="I31" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="J31" t="s">
         <v>19</v>
@@ -5290,13 +5362,13 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="B32" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="D32" t="s">
         <v>14</v>
@@ -5311,10 +5383,10 @@
         <v>17</v>
       </c>
       <c r="H32">
-        <v>239128</v>
+        <v>204142</v>
       </c>
       <c r="I32" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="J32" t="s">
         <v>19</v>
@@ -5325,13 +5397,13 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="B33" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C33" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="D33" t="s">
         <v>14</v>
@@ -5346,10 +5418,10 @@
         <v>17</v>
       </c>
       <c r="H33">
-        <v>231464</v>
+        <v>254491</v>
       </c>
       <c r="I33" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="J33" t="s">
         <v>19</v>
@@ -5360,13 +5432,13 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C34" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="D34" t="s">
         <v>14</v>
@@ -5381,10 +5453,10 @@
         <v>17</v>
       </c>
       <c r="H34">
-        <v>254978</v>
+        <v>81698</v>
       </c>
       <c r="I34" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="J34" t="s">
         <v>19</v>
@@ -5395,13 +5467,13 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C35" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="D35" t="s">
         <v>14</v>
@@ -5416,10 +5488,10 @@
         <v>17</v>
       </c>
       <c r="H35">
-        <v>157984</v>
+        <v>168546</v>
       </c>
       <c r="I35" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="J35" t="s">
         <v>19</v>
@@ -5430,13 +5502,13 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C36" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="D36" t="s">
         <v>14</v>
@@ -5451,10 +5523,10 @@
         <v>17</v>
       </c>
       <c r="H36">
-        <v>177855</v>
+        <v>186103</v>
       </c>
       <c r="I36" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="J36" t="s">
         <v>19</v>
@@ -5523,13 +5595,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="B2" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="C2" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -5544,10 +5616,10 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>118307</v>
+        <v>141245</v>
       </c>
       <c r="I2" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -5616,13 +5688,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="B2" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="C2" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -5637,10 +5709,10 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>158540</v>
+        <v>165632</v>
       </c>
       <c r="I2" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -5709,13 +5781,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="B2" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C2" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -5730,10 +5802,10 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>280835</v>
+        <v>160292</v>
       </c>
       <c r="I2" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -5744,13 +5816,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="B3" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C3" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -5765,10 +5837,10 @@
         <v>17</v>
       </c>
       <c r="H3">
-        <v>136992</v>
+        <v>196377</v>
       </c>
       <c r="I3" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -5779,13 +5851,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="B4" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C4" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -5800,10 +5872,10 @@
         <v>17</v>
       </c>
       <c r="H4">
-        <v>114230</v>
+        <v>206980</v>
       </c>
       <c r="I4" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -5814,13 +5886,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="B5" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C5" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -5835,10 +5907,10 @@
         <v>17</v>
       </c>
       <c r="H5">
-        <v>204390</v>
+        <v>224895</v>
       </c>
       <c r="I5" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
@@ -5849,13 +5921,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="B6" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C6" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -5870,10 +5942,10 @@
         <v>17</v>
       </c>
       <c r="H6">
-        <v>152641</v>
+        <v>227326</v>
       </c>
       <c r="I6" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -5884,13 +5956,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="B7" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C7" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -5905,10 +5977,10 @@
         <v>17</v>
       </c>
       <c r="H7">
-        <v>100692</v>
+        <v>278128</v>
       </c>
       <c r="I7" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -5919,13 +5991,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="B8" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C8" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -5940,10 +6012,10 @@
         <v>17</v>
       </c>
       <c r="H8">
-        <v>297392</v>
+        <v>86892</v>
       </c>
       <c r="I8" t="s">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -5954,13 +6026,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="B9" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C9" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -5975,10 +6047,10 @@
         <v>17</v>
       </c>
       <c r="H9">
-        <v>295451</v>
+        <v>273486</v>
       </c>
       <c r="I9" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
@@ -5989,13 +6061,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="B10" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C10" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -6010,10 +6082,10 @@
         <v>17</v>
       </c>
       <c r="H10">
-        <v>104826</v>
+        <v>249288</v>
       </c>
       <c r="I10" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="J10" t="s">
         <v>19</v>
@@ -6024,13 +6096,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="B11" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C11" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -6045,10 +6117,10 @@
         <v>17</v>
       </c>
       <c r="H11">
-        <v>278716</v>
+        <v>264433</v>
       </c>
       <c r="I11" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="J11" t="s">
         <v>19</v>
@@ -6117,13 +6189,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="B2" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C2" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -6138,10 +6210,10 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>195185</v>
+        <v>103887</v>
       </c>
       <c r="I2" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -6152,13 +6224,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="B3" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C3" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -6173,10 +6245,10 @@
         <v>17</v>
       </c>
       <c r="H3">
-        <v>251639</v>
+        <v>176354</v>
       </c>
       <c r="I3" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -6187,13 +6259,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="B4" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C4" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -6208,10 +6280,10 @@
         <v>17</v>
       </c>
       <c r="H4">
-        <v>216749</v>
+        <v>75838</v>
       </c>
       <c r="I4" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -6222,13 +6294,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="B5" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C5" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -6243,10 +6315,10 @@
         <v>17</v>
       </c>
       <c r="H5">
-        <v>130607</v>
+        <v>232500</v>
       </c>
       <c r="I5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
@@ -6257,13 +6329,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="B6" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C6" t="s">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -6278,10 +6350,10 @@
         <v>17</v>
       </c>
       <c r="H6">
-        <v>69733</v>
+        <v>135849</v>
       </c>
       <c r="I6" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -6292,13 +6364,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="B7" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C7" t="s">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -6313,10 +6385,10 @@
         <v>17</v>
       </c>
       <c r="H7">
-        <v>86814</v>
+        <v>258877</v>
       </c>
       <c r="I7" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -6327,13 +6399,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="B8" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C8" t="s">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -6348,10 +6420,10 @@
         <v>17</v>
       </c>
       <c r="H8">
-        <v>196526</v>
+        <v>271321</v>
       </c>
       <c r="I8" t="s">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -6362,13 +6434,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="B9" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C9" t="s">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -6383,10 +6455,10 @@
         <v>17</v>
       </c>
       <c r="H9">
-        <v>197330</v>
+        <v>289892</v>
       </c>
       <c r="I9" t="s">
-        <v>329</v>
+        <v>353</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
@@ -6397,13 +6469,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="B10" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C10" t="s">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -6418,10 +6490,10 @@
         <v>17</v>
       </c>
       <c r="H10">
-        <v>179446</v>
+        <v>149078</v>
       </c>
       <c r="I10" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="J10" t="s">
         <v>19</v>
@@ -6432,13 +6504,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>331</v>
+        <v>354</v>
       </c>
       <c r="B11" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C11" t="s">
-        <v>332</v>
+        <v>357</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -6453,10 +6525,10 @@
         <v>17</v>
       </c>
       <c r="H11">
-        <v>178023</v>
+        <v>174735</v>
       </c>
       <c r="I11" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
       <c r="J11" t="s">
         <v>19</v>
@@ -6467,13 +6539,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="B12" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C12" t="s">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
@@ -6488,10 +6560,10 @@
         <v>17</v>
       </c>
       <c r="H12">
-        <v>148749</v>
+        <v>235660</v>
       </c>
       <c r="I12" t="s">
-        <v>336</v>
+        <v>360</v>
       </c>
       <c r="J12" t="s">
         <v>19</v>
@@ -6502,13 +6574,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="B13" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C13" t="s">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -6523,10 +6595,10 @@
         <v>17</v>
       </c>
       <c r="H13">
-        <v>227970</v>
+        <v>247487</v>
       </c>
       <c r="I13" t="s">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="J13" t="s">
         <v>19</v>
@@ -6537,13 +6609,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="B14" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C14" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="D14" t="s">
         <v>14</v>
@@ -6558,10 +6630,10 @@
         <v>17</v>
       </c>
       <c r="H14">
-        <v>171614</v>
+        <v>178214</v>
       </c>
       <c r="I14" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="J14" t="s">
         <v>19</v>
@@ -6572,13 +6644,13 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="B15" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C15" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -6593,10 +6665,10 @@
         <v>17</v>
       </c>
       <c r="H15">
-        <v>141306</v>
+        <v>142671</v>
       </c>
       <c r="I15" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="J15" t="s">
         <v>19</v>
@@ -6607,13 +6679,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>344</v>
+        <v>368</v>
       </c>
       <c r="B16" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C16" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="D16" t="s">
         <v>14</v>
@@ -6628,10 +6700,10 @@
         <v>17</v>
       </c>
       <c r="H16">
-        <v>192282</v>
+        <v>260310</v>
       </c>
       <c r="I16" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="J16" t="s">
         <v>19</v>
